--- a/data/trans_orig/IP1002-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP1002-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>707</t>
+          <t>705</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6504</t>
+          <t>6636</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4856</t>
+          <t>4353</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1747</t>
+          <t>1409</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7979</t>
+          <t>7742</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>132222</t>
+          <t>132090</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>138019</t>
+          <t>138021</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>148221</t>
+          <t>148724</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>283824</t>
+          <t>284061</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>290056</t>
+          <t>290394</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,52%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1255</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7479</t>
+          <t>7530</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>666</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5407</t>
+          <t>5040</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>2987</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9929</t>
+          <t>10622</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>187684</t>
+          <t>187633</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>193908</t>
+          <t>193899</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>206735</t>
+          <t>207102</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>211475</t>
+          <t>211476</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>397376</t>
+          <t>396683</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>404660</t>
+          <t>404318</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>446</t>
+          <t>445</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4674</t>
+          <t>4860</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4236</t>
+          <t>4751</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1168</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7496</t>
+          <t>6712</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>133143</t>
+          <t>132957</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>137371</t>
+          <t>137372</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>145421</t>
+          <t>144906</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>279978</t>
+          <t>280762</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>286306</t>
+          <t>286303</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5977</t>
+          <t>5701</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1406</t>
+          <t>1411</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8944</t>
+          <t>8266</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2340</t>
+          <t>2267</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10972</t>
+          <t>10933</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>203338</t>
+          <t>203614</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>198880</t>
+          <t>199558</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>206418</t>
+          <t>206413</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>406167</t>
+          <t>406206</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>414799</t>
+          <t>414872</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,46%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4955</t>
+          <t>5571</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14993</t>
+          <t>15385</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4393</t>
+          <t>4825</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13975</t>
+          <t>14763</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11998</t>
+          <t>12396</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27440</t>
+          <t>25768</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>666028</t>
+          <t>665636</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>676066</t>
+          <t>675450</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>708725</t>
+          <t>707937</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>718307</t>
+          <t>717875</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1376281</t>
+          <t>1377953</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1391723</t>
+          <t>1391325</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,12%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>673</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6354</t>
+          <t>6547</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2070</t>
+          <t>2112</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10240</t>
+          <t>9543</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3575</t>
+          <t>3586</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12742</t>
+          <t>13085</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>130037</t>
+          <t>129844</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>135710</t>
+          <t>135718</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>142858</t>
+          <t>143555</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>151028</t>
+          <t>150986</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>276747</t>
+          <t>276404</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>285914</t>
+          <t>285903</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,76%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8492</t>
+          <t>7507</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3043,7 +3043,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2697</t>
+          <t>2773</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10622</t>
+          <t>10823</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5051</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15603</t>
+          <t>14975</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>196906</t>
+          <t>197891</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>204102</t>
+          <t>204103</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>211355</t>
+          <t>211154</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>219280</t>
+          <t>219204</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>411773</t>
+          <t>412401</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>422325</t>
+          <t>422298</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,81%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1131</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6684</t>
+          <t>7095</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>1949</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9734</t>
+          <t>9605</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4459</t>
+          <t>4453</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13598</t>
+          <t>13583</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>148155</t>
+          <t>147744</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>153708</t>
+          <t>153714</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>156251</t>
+          <t>156380</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>164010</t>
+          <t>164036</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>307226</t>
+          <t>307241</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>316365</t>
+          <t>316371</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>566</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5922</t>
+          <t>6156</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>667</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6120</t>
+          <t>6149</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1498</t>
+          <t>1634</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9010</t>
+          <t>8571</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>204378</t>
+          <t>204144</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>209735</t>
+          <t>209734</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>200962</t>
+          <t>200933</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>206416</t>
+          <t>206415</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>408372</t>
+          <t>408811</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>415884</t>
+          <t>415748</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,61%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5958</t>
+          <t>6422</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17024</t>
+          <t>17518</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12635</t>
+          <t>11606</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27606</t>
+          <t>26197</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21118</t>
+          <t>20506</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38755</t>
+          <t>37721</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>689904</t>
+          <t>689410</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>700970</t>
+          <t>700506</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>720536</t>
+          <t>721945</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>735507</t>
+          <t>736536</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1416315</t>
+          <t>1417349</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1433952</t>
+          <t>1434564</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,59%</t>
         </is>
       </c>
     </row>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4301</t>
+          <t>4218</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3289</t>
+          <t>3331</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>584</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5023</t>
+          <t>5088</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4717,7 +4717,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>129406</t>
+          <t>129489</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>144787</t>
+          <t>144745</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>276760</t>
+          <t>276695</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>281205</t>
+          <t>281199</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1068</t>
+          <t>696</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6421</t>
+          <t>6255</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>2036</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8991</t>
+          <t>9681</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3901</t>
+          <t>4150</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13376</t>
+          <t>12691</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>200826</t>
+          <t>200992</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>206179</t>
+          <t>206551</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>215368</t>
+          <t>214678</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>222369</t>
+          <t>222323</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>418230</t>
+          <t>418915</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>427705</t>
+          <t>427456</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,04%</t>
         </is>
       </c>
     </row>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4471</t>
+          <t>4469</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>676</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5791</t>
+          <t>6447</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1391</t>
+          <t>1458</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7988</t>
+          <t>8647</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>151526</t>
+          <t>151528</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>160882</t>
+          <t>160226</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>166037</t>
+          <t>165997</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>314682</t>
+          <t>314023</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>321279</t>
+          <t>321212</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>720</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6421</t>
+          <t>6981</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>689</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6331</t>
+          <t>5758</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2128</t>
+          <t>1501</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9769</t>
+          <t>9144</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>200999</t>
+          <t>200439</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>206703</t>
+          <t>206700</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>199405</t>
+          <t>199978</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>205053</t>
+          <t>205047</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>403387</t>
+          <t>404012</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>411028</t>
+          <t>411655</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,64%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3992</t>
+          <t>4151</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12658</t>
+          <t>13589</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5957</t>
+          <t>6091</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16412</t>
+          <t>16307</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,47 +6049,47 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>17791</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>11636</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>25341</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>0,8%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>2,2%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>17791</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>12131</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>25866</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>691713</t>
+          <t>690782</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>700379</t>
+          <t>700220</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>728432</t>
+          <t>728537</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>738887</t>
+          <t>738753</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,47 +6162,47 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
+          <t>99,18%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>2099</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>1431424</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>1423874</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>1437579</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>98,77%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>98,25%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
           <t>99,2%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>2099</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>1431424</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>1423349</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>1437084</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>98,77%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>98,22%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>99,16%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>627</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7297</t>
+          <t>8586</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6614,7 +6614,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8987</t>
+          <t>9185</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1649</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11891</t>
+          <t>11085</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>109983</t>
+          <t>108694</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>116658</t>
+          <t>116653</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,7 +6702,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>130423</t>
+          <t>130225</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>244799</t>
+          <t>245605</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>255041</t>
+          <t>255197</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,42%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>380</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4355</t>
+          <t>4876</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>817</t>
+          <t>822</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7663</t>
+          <t>7693</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1597</t>
+          <t>1620</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9449</t>
+          <t>8839</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>186157</t>
+          <t>185636</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>190131</t>
+          <t>190132</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>247372</t>
+          <t>247342</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>254218</t>
+          <t>254213</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>436099</t>
+          <t>436709</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>443951</t>
+          <t>443928</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,7 +7115,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1174</t>
+          <t>1016</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8569</t>
+          <t>8037</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1341</t>
+          <t>1448</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10958</t>
+          <t>11163</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3650</t>
+          <t>3889</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14141</t>
+          <t>15501</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>181016</t>
+          <t>181548</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>188411</t>
+          <t>188569</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>174328</t>
+          <t>174123</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>183945</t>
+          <t>183838</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>360730</t>
+          <t>359370</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>371221</t>
+          <t>370982</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4071</t>
+          <t>4169</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7643,7 +7643,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4431</t>
+          <t>4777</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>835</t>
+          <t>596</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6108</t>
+          <t>6123</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,7 +7688,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>163891</t>
+          <t>163793</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -7731,7 +7731,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7751,7 +7751,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>176807</t>
+          <t>176461</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>343093</t>
+          <t>343078</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>348366</t>
+          <t>348605</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,83%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4649</t>
+          <t>5037</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14870</t>
+          <t>15481</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5837</t>
+          <t>5675</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18656</t>
+          <t>19366</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11584</t>
+          <t>12932</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28318</t>
+          <t>29264</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>650470</t>
+          <t>649859</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>660691</t>
+          <t>660303</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>742313</t>
+          <t>741603</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>755132</t>
+          <t>755294</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1397991</t>
+          <t>1397045</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1414725</t>
+          <t>1413377</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,09%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP1002-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP1002-Habitat-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1329</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4736</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3,09%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>2630</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>705</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6636</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>709</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>6903</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>1,9%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,51%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,78%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1329</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4353</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1409</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7742</t>
+          <t>8222</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -836,74 +836,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>151748</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>148341</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,13%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>96,91%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>199</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>136096</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>132090</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>138021</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>131823</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>138017</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>98,1%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>95,22%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>95,02%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>99,49%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>151748</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>148724</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,13%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>97,16%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>423</t>
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>284061</t>
+          <t>283581</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>290394</t>
+          <t>290468</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,54%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5282</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,49%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>3570</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1264</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>7530</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1257</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>7651</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,83%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,86%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>666</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5040</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2987</t>
+          <t>3009</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10622</t>
+          <t>10400</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>319</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>210116</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>206860</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>211477</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,04%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>97,51%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,69%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>306</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>191593</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>187633</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>193899</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>187512</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>193906</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>98,17%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96,14%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,35%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>319</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>210116</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>207102</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>211476</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,04%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>396683</t>
+          <t>396905</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>404318</t>
+          <t>404296</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,26%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>312</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1375</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4894</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3,27%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1742</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>445</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4860</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4709</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>1,26%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,53%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1375</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4751</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6712</t>
+          <t>7149</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>148282</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>144763</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,08%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>96,73%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>136075</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>132957</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>137372</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>133108</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>137369</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>98,74%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>96,47%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>99,68%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>148282</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>144906</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,08%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>280762</t>
+          <t>280325</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>286303</t>
+          <t>286402</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,63%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3791</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1413</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>9108</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,38%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1641</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5701</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>6429</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,78%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,72%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3791</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1411</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>8266</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2267</t>
+          <t>2306</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10933</t>
+          <t>10704</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -1865,74 +1865,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>204033</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>198716</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>206411</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,18%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>95,62%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,32%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>207674</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>203614</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>202886</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,22%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>97,28%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>96,93%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>204033</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>199558</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>206413</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,18%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>96,02%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,32%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>573</t>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>406206</t>
+          <t>406435</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>414872</t>
+          <t>414833</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,45%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>8521</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4177</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>15357</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,18%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2,12%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>9584</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>5571</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>15385</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>5199</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>14993</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,41%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,26%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>8521</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>4825</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>14763</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12396</t>
+          <t>12002</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25768</t>
+          <t>25622</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1074</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>714179</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>707343</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>718523</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,82%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>97,88%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,42%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1003</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>671437</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>665636</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>675450</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>666028</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>675822</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>98,59%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>97,74%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,18%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1074</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>714179</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>707937</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>717875</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,82%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1377953</t>
+          <t>1378099</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1391325</t>
+          <t>1391719</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,14%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2154</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>10090</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3,32%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>6,59%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>2284</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>673</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6547</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>677</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>6282</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>1,67%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,8%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>5090</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2112</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>9543</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>3,32%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3586</t>
+          <t>3607</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13085</t>
+          <t>13215</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>148008</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>143008</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>150944</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>96,68%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>93,41%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>98,59%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>182</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>134107</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>129844</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>135718</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>130109</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>135714</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>98,33%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>95,2%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>99,51%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>148008</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>143555</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>150986</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>96,68%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>276404</t>
+          <t>276274</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>285903</t>
+          <t>285882</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,75%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>153098</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>153098</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>153098</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>185</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>136391</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>136391</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>136391</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>153098</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>153098</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>153098</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5854</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2753</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>10895</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2,64%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,24%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4,91%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>3385</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1295</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>7507</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1319</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>7419</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,65%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,65%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>5854</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>2773</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>10823</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,64%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>5051</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14975</t>
+          <t>16014</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>313</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>216123</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>211082</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>219224</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>97,36%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>95,09%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,76%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>312</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>202013</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>197891</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>204103</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>197979</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>204079</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>98,35%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96,35%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,37%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>313</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>216123</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>211154</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>219204</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>97,36%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>412401</t>
+          <t>411362</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>422298</t>
+          <t>422325</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,82%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>221977</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>221977</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>221977</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>317</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>205398</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>205398</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>205398</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>321</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>221977</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>221977</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>221977</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4810</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2196</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9791</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,9%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>5,9%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>3028</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1125</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7095</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1128</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>6633</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>1,96%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,73%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,58%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>4810</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1949</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>9605</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,9%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4453</t>
+          <t>4465</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13583</t>
+          <t>13311</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -3469,74 +3469,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>161175</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>156194</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>163789</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>97,1%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>94,1%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,68%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>236</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>151811</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>147744</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>153714</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>148206</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>153711</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>98,04%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>95,42%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>95,72%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>99,27%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>161175</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>156380</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>164036</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>97,1%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>94,21%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>98,83%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>484</t>
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>307241</t>
+          <t>307513</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>316371</t>
+          <t>316359</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>154839</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>154839</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>154839</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3704,67 +3704,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>2133</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>668</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6504</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,14%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>2080</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>566</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6156</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5976</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,99%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,27%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,93%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2133</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>667</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>6149</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1634</t>
+          <t>1406</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8571</t>
+          <t>8832</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -3812,74 +3812,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>278</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>204949</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>200578</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>206414</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,97%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>96,86%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,68%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>208220</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>204144</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>204324</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>209734</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,01%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>97,07%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>97,16%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>99,73%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>278</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>204949</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>200933</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>206415</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,97%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>97,03%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,68%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>550</t>
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>408811</t>
+          <t>408550</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>415748</t>
+          <t>415976</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,66%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>207082</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>207082</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>207082</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>275</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>207082</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>207082</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>207082</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>17887</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>11363</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>25718</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2,39%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3,44%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>10777</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>6422</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>17518</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>6421</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>17680</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,52%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,91%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,48%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>17887</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>11606</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>26197</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>2,39%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20506</t>
+          <t>21163</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>37721</t>
+          <t>38840</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -4155,74 +4155,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1041</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>730255</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>722424</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>736779</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>97,61%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>96,56%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>98,48%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1002</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>696151</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>689410</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>700506</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>689248</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>700507</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>98,48%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>97,52%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>97,5%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>99,09%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1041</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>730255</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>721945</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>736536</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>97,61%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>96,5%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>98,45%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>2043</t>
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1417349</t>
+          <t>1416230</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1434564</t>
+          <t>1433907</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,55%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1066</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3525</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2,38%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1213</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4218</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3734</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,91%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,15%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>652</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3331</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>579</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5088</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4717,7 +4717,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -4730,74 +4730,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>147424</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>144551</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,56%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>97,62%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>185</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>132494</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>129489</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>129973</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>99,09%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>96,85%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>97,21%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>147424</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>144745</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,56%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>97,75%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>379</t>
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>276695</t>
+          <t>276845</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>281199</t>
+          <t>281204</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4689</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>9084</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4,05%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>2904</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>696</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>6255</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1068</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>6783</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,4%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,02%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>4689</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>2036</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>9681</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,09%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4150</t>
+          <t>4102</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12691</t>
+          <t>12522</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>325</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>219670</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>215275</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>222354</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>97,91%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>95,95%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,11%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>329</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>204343</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>200992</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>206551</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>200464</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>206179</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>98,6%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96,98%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,66%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>325</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>219670</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>214678</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>222323</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>97,91%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>418915</t>
+          <t>419084</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>427456</t>
+          <t>427504</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,05%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>334</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2588</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>637</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6479</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3,89%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1211</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4469</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4171</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,78%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,86%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2588</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>676</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>6447</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1458</t>
+          <t>1679</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8647</t>
+          <t>7620</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -5416,74 +5416,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>164085</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>160194</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>166036</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,45%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>96,11%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,62%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>257</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>154786</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>151528</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>151826</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,22%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>97,14%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>97,33%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>164085</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>160226</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>165997</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,45%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>96,13%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>99,59%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>501</t>
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>314023</t>
+          <t>315050</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>321212</t>
+          <t>320991</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>259</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5651,87 +5651,87 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>2148</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>682</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5707</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,77%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>2386</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6981</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>724</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>6688</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,15%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,35%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,37%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>3,22%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>4534</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>2148</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>689</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5758</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>2,8%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>4534</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>1501</t>
-        </is>
-      </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9144</t>
+          <t>9509</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -5759,74 +5759,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>203588</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>200029</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>205054</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,96%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97,23%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,67%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>278</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>205034</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>200439</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>206700</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>200732</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>206696</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,85%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>96,63%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>96,78%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>99,65%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>287</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>203588</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>199978</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>205047</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,96%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>97,2%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,67%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>565</t>
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>404012</t>
+          <t>403647</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>411655</t>
+          <t>411008</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>281</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>10077</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>6040</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>16584</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>7714</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>4151</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>13589</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>3827</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>12962</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,1%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,93%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>10077</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>6091</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>16307</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11636</t>
+          <t>12253</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25341</t>
+          <t>25723</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1050</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>734767</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>728260</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>738804</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,65%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>97,77%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,19%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1049</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>696657</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>690782</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>700220</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>691409</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>700544</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>98,9%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>98,07%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,41%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1050</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>734767</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>728537</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>738753</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,65%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1423874</t>
+          <t>1423492</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1437579</t>
+          <t>1436962</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1740</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6462</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>5,17%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2575</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>627</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8586</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,2%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>7,32%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2371</t>
+          <t>2590</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>626</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9185</t>
+          <t>7257</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>4945</t>
+          <t>4330</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>1533</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11085</t>
+          <t>10129</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>123214</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>118492</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>124954</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>98,61%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>94,83%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>193</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>114705</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>108694</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>116653</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>97,8%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>92,68%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>99,47%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>137039</t>
+          <t>118481</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>130225</t>
+          <t>113814</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>139410</t>
+          <t>120445</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>251745</t>
+          <t>241695</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>245605</t>
+          <t>235896</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>255197</t>
+          <t>244492</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>124954</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>124954</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>124954</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>139410</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>139410</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>139410</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>256690</t>
+          <t>246025</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>256690</t>
+          <t>246025</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>256690</t>
+          <t>246025</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1536</t>
+          <t>2684</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>853</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4876</t>
+          <t>7974</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2532</t>
+          <t>1553</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>338</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7693</t>
+          <t>4905</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>4068</t>
+          <t>4237</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1620</t>
+          <t>1733</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8839</t>
+          <t>9936</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>234522</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>229232</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>236353</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,87%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96,64%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,64%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>277</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>188976</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>185636</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>190132</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>99,19%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>97,44%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,8%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>340</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>252503</t>
+          <t>182860</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>247342</t>
+          <t>179508</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>254213</t>
+          <t>184075</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>441480</t>
+          <t>417382</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>436709</t>
+          <t>411683</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>443928</t>
+          <t>419886</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,59%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>280</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>343</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3419</t>
+          <t>4109</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1016</t>
+          <t>1225</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8037</t>
+          <t>10513</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4307</t>
+          <t>3468</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1448</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11163</t>
+          <t>8291</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>7726</t>
+          <t>7577</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3889</t>
+          <t>3488</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15501</t>
+          <t>14806</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>164232</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>157828</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>167116</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>97,56%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>93,75%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,27%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>221</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>186166</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>181548</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>188569</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>98,2%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>95,76%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>99,46%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>180979</t>
+          <t>152736</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>174123</t>
+          <t>147913</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>183838</t>
+          <t>154972</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>367145</t>
+          <t>316968</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>359370</t>
+          <t>309739</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>370982</t>
+          <t>321057</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,93%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>189585</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>189585</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>189585</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>156204</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>156204</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>156204</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>374871</t>
+          <t>324545</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>374871</t>
+          <t>324545</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>374871</t>
+          <t>324545</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,7 +7598,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1169</t>
+          <t>1343</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -7608,92 +7608,92 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4169</t>
+          <t>4538</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,68%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1017</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3231</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>1,93%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>852</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>6185</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
           <t>0,7%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,48%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1445</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4777</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>2,64%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>2614</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>596</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>6123</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -7706,107 +7706,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>168033</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>164838</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,21%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97,32%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>238</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>166793</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>163793</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>166128</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>163914</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>167145</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>99,39%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>98,07%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>474</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>334161</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>330336</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>335669</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
         <is>
           <t>99,3%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>97,52%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>179793</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>176461</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>181238</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,2%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>97,36%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>474</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>346587</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>343078</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>348605</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>99,25%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,75%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>240</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>9876</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>5041</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>17203</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,72%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2,46%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>8698</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>5037</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>15481</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,33%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>10656</t>
+          <t>8628</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5675</t>
+          <t>4524</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19366</t>
+          <t>15265</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,27 +8011,27 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>19354</t>
+          <t>18504</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12932</t>
+          <t>11820</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29264</t>
+          <t>27210</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>964</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>690001</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>682674</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>694836</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,59%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>97,54%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,28%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>929</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>656642</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>649859</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>660303</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>98,69%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>97,67%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,24%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>964</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>750313</t>
+          <t>620205</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>741603</t>
+          <t>613568</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>755294</t>
+          <t>624309</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,22 +8124,22 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1406955</t>
+          <t>1310206</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1397045</t>
+          <t>1301500</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1413377</t>
+          <t>1316890</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -8149,7 +8149,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,11%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>699877</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>699877</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>699877</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>942</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>760969</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>760969</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>760969</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1426309</t>
+          <t>1328710</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1426309</t>
+          <t>1328710</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1426309</t>
+          <t>1328710</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
